--- a/Digital Ceasefire Platform.xlsx
+++ b/Digital Ceasefire Platform.xlsx
@@ -15,11 +15,6 @@
     <sheet name="law_clauses" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="footnotes" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="posts" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="registrations" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="reviewers" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="feedback" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="reviewers_public" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="feedback_public" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +517,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Digital Ceasefire &amp; Deescalation Handbook</t>
+          <t>Digital Ceasefire &amp; De-escalation Handbook</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -535,7 +530,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A working framework mediators, negotiators, and conflict parties can use to negotiate and draft the Digital components of ceasefire and deescalation agreements.</t>
+          <t>A practical framework for mediators, negotiators, and affected communities to negotiate, draft, and implement ceasefire, de-escalation, and other agreements to constrain digital operations during conflict and other security contexts.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -577,46 +572,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>home.cta_review</t>
+          <t>home.category_internet_interference</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Become a Reviewer</t>
+          <t>Internet Interference</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Button to registration form</t>
+          <t>One of the three prohibited-operations categories, shown on Home</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>home.category_internet_interference</t>
+          <t>home.category_internet_interference.desc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Internet Interference</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>One of the three prohibited-operations categories, shown on Home</t>
-        </is>
-      </c>
+          <t>Shutdowns, attacks on infrastructure, and jamming that cut people off from the internet.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>home.category_internet_interference.desc</t>
+          <t>home.category_information_threats</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shutdowns, attacks on infrastructure, and jamming that cut people off from the internet.</t>
+          <t>Information Threats</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -624,12 +615,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>home.category_information_threats</t>
+          <t>home.category_information_threats.desc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Threats</t>
+          <t>Disinformation, hate speech, incitement, doxxing, and manipulated media used to escalate conflict.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -637,12 +628,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>home.category_information_threats.desc</t>
+          <t>home.category_cyber_attacks</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Disinformation, hate speech, incitement, doxxing, and manipulated media used to escalate conflict.</t>
+          <t>Cyber Attacks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -650,12 +641,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>home.category_cyber_attacks</t>
+          <t>home.category_cyber_attacks.desc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cyber Attacks</t>
+          <t>Hacking, malware, DDoS, phishing, and surveillance directed at people and infrastructure.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -663,12 +654,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>home.category_cyber_attacks.desc</t>
+          <t>builder.library_title</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hacking, malware, DDoS, phishing, and surveillance directed at people and infrastructure.</t>
+          <t>Provision library</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -676,80 +667,68 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>builder.library_search_placeholder</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NGO / civil society|Lawyer / legal scholar|Technical expert|Mediator / negotiator|Government|International organization|Academic|Other</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Fixed reviewer role list, pipe-separated, used by the registration form and role badges</t>
-        </is>
-      </c>
+          <t>Search provisions...</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>context.armed_conflict.example</t>
+          <t>builder.agreement_title</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>e.g. an international or non-international Armed Conflict under International Humanitarian Law.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>One-line example shown under the Armed Conflict option in Builder step 1</t>
-        </is>
-      </c>
+          <t>Your agreement</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>context.grey_zone.example</t>
+          <t>builder.add_button</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>e.g. coercive or destabilizing activity below the threshold of Armed Conflict.</t>
+          <t>Add to my agreement</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Builder step 1</t>
+          <t>Button in the handbook reader and the library</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>context.internal_disturbance.example</t>
+          <t>builder.added_badge</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>e.g. serious internal disorder, such as riots, that does not amount to Armed Conflict.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Builder step 1</t>
-        </is>
-      </c>
+          <t>Added</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>builder.step1_title</t>
+          <t>builder.suggested_badge</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What kind of situation is this agreement for?</t>
+          <t>Suggested for this context</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -757,12 +736,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>builder.step1_help</t>
+          <t>builder.edited_badge</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>This sets which provisions are suggested first. You can change it later in Settings.</t>
+          <t>Edited</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -770,12 +749,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>builder.start_empty</t>
+          <t>builder.restore_original</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Start empty instead</t>
+          <t>Restore original text</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -783,12 +762,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>builder.continue</t>
+          <t>builder.remove</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Continue</t>
+          <t>Remove</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -796,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>builder.library_title</t>
+          <t>builder.add_custom_provision</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Provision library</t>
+          <t>Add a custom provision</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -809,12 +788,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>builder.library_search_placeholder</t>
+          <t>builder.add_custom_definition</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Search provisions...</t>
+          <t>Add a custom definition</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -822,42 +801,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>builder.agreement_title</t>
+          <t>builder.pin</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Your agreement</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>Pin</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Keep an auto-attached definition/law clause even if unused</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>builder.add_button</t>
+          <t>builder.unpin</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Add to my agreement</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Button in the handbook reader and the library</t>
-        </is>
-      </c>
+          <t>Unpin</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>builder.added_badge</t>
+          <t>builder.settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Added</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -865,25 +844,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>builder.suggested_badge</t>
+          <t>builder.parties_label</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Suggested for this context</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>Parties</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Settings panel: list of party names filling [Party A] etc.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>builder.edited_badge</t>
+          <t>builder.entry_into_force_label</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Edited</t>
+          <t>Entry into force</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -891,12 +874,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>builder.restore_original</t>
+          <t>builder.saved_indicator</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Restore original text</t>
+          <t>Saved</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -904,12 +887,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>builder.remove</t>
+          <t>builder.new_draft</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Remove</t>
+          <t>New draft</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -917,12 +900,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>builder.add_custom_provision</t>
+          <t>builder.export_docx</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Add a custom provision</t>
+          <t>Export as Word (.docx)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -930,12 +913,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>builder.add_custom_definition</t>
+          <t>builder.export_markdown</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Add a custom definition</t>
+          <t>Export as Markdown</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -943,42 +926,42 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>builder.pin</t>
+          <t>builder.export_print</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pin</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Keep an auto-attached definition/law clause even if unused</t>
-        </is>
-      </c>
+          <t>Print / Save as PDF</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>builder.unpin</t>
+          <t>builder.export_signature_block</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Unpin</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Export section heading</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>builder.settings</t>
+          <t>builder.export_definitions_heading</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Definitions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -986,29 +969,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>builder.parties_label</t>
+          <t>builder.export_annex_heading</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Parties</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Settings panel: list of party names filling [Party A] etc.</t>
-        </is>
-      </c>
+          <t>Annex on Commitment to International Law</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>builder.entry_into_force_label</t>
+          <t>builder.undefined_terms_warning</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Entry into force</t>
+          <t>These capitalized terms are used in your agreement but have no definition:</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1016,12 +995,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>builder.saved_indicator</t>
+          <t>footer.data_source</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Saved</t>
+          <t>Content is maintained by the Digital Ceasefire Initiative and updates automatically.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1029,12 +1008,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>builder.new_draft</t>
+          <t>footer.disclaimer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New draft</t>
+          <t>This tool assembles model language for discussion. It is not legal advice.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1042,249 +1021,322 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>builder.export_docx</t>
+          <t>home.cta_read.desc</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Export as Word (.docx)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Browse the full text of the Handbook, section by section.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Home card description</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>builder.export_markdown</t>
+          <t>home.cta_build.desc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Export as Markdown</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>Assemble a customized ceasefire, de-escalation, or other agreement from the available provisions.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Home card description</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>builder.export_print</t>
+          <t>home.cta_updates.desc</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Print / Save as PDF</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>See the latest posts, news and updates to the Platform.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Home card description</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>builder.include_footnotes</t>
+          <t>nav.about</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Include footnotes</t>
+          <t>About</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Export toggle</t>
+          <t>Header nav item</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>builder.export_signature_block</t>
+          <t>about.title</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Signatures</t>
+          <t>About</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Export section heading</t>
+          <t>About page heading</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>builder.export_definitions_heading</t>
+          <t>about.body</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Definitions</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>The Digital Ceasefire &amp; De-escalation Handbook provides a practical framework for mediators, negotiators, and affected communities to negotiate, draft, and implement ceasefire, de-escalation, and other agreements that constrain digital operations in conflict and other security contexts.
+Developed in response to the accelerating digitalization of warfare, the Platform addresses the urgent need to confront hostile digital operations. Ceasefire agreements have traditionally overlooked the digital dimensions of conflict, leaving gaps in civilian protection and allowing unconstrained digital operations to take place.
+The Platform addresses three interconnected dimensions of digital warfare: Internet Interference; Information Threats; and Cyber Attacks. It places the experiences and protection of conflict-affected populations at the center of its approach.
+Grounded in International Law, including International Humanitarian Law, International Human Rights Law, and International Criminal Law, the Platform recognizes the challenges of applying existing legal frameworks to evolving digital threats. While Parties remain bound by their obligations under International Law, the Platform enables them to negotiate additional commitments to restrain and de-escalate digital operations that may otherwise be lawful.
+At its core is the Digital Ceasefire &amp; De-escalation Handbook, a living resource designed to evolve alongside technological developments, emerging threats, and lessons from practice. Rather than prescribing a single solution, the Handbook offers a flexible menu of model provisions that Parties can select, adapt, and combine to develop agreements tailored to different conflict and security contexts.
+Through the Platform's [Build an Agreement function](#/builder), users can construct customized agreements using the Handbook's model provisions. The [Note to Users](#/handbook/s-note-to-users) provides useful background to constructing an Agreement. Alternatively, the [entire handbook](#/handbook) can be read and used here as a guide to support and contribute to existing negotiations.
+### Background to the Initiative
+The Digital Ceasefire &amp; De-escalation Platform is an initiative of the Human Rights Center at the University of California, Berkeley School of Law, and is co-led by Senior Research Fellow Brett Solomon and Executive Director Betsy Popken. The Handbook has been informed by research, consultations, and engagement with experts and practitioners working across conflict mediation and negotiation, international law, human rights, humanitarian protection, and digital technologies.
+The initiative seeks to bridge the gap between the rapidly evolving realities of digital warfare and the practical tools available to those working to prevent conflict, reduce hostilities, protect civilians, and advance Digital Peace.
+The Digital Ceasefire team is available to provide advice, technical assistance, briefings, training, and support to mediators, negotiators, civil society organizations, and others addressing the digital dimensions of conflict.
+The website was created by the Investigations Lab, Human Rights Center. **AI Disclosure:** This platform was created using a combination of cloud and local models and LLM harnesses. All the text was produced by humans.
+Contact: Betsy Popken at [bpopken@berkeley.edu](mailto:bpopken@berkeley.edu) or Brett Solomon at [solomonbrett@gmail.com](mailto:solomonbrett@gmail.com)
+[Explore the Handbook](#/handbook) | [Build an Agreement](#/builder) | [Request Support](mailto:bpopken@berkeley.edu)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>About page body (Markdown)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>builder.export_annex_heading</t>
+          <t>handbook.intro</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Annex on Commitment to International Law</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>The full text of the Digital Ceasefire &amp; De-escalation Handbook is available here, section by section, or it can be downloaded in full in [PDF format](#handbook-pdf). The Handbook guides users through the process of developing an Agreement, either by selecting appropriate provisions of the Handbook into an Agreement or by using the Platform's [Build an Agreement function](#/builder). We recommend starting with reading the [Note to Users](#/handbook/s-note-to-users) below. Sections 1.0 through 11.0 then provide model provisions that can be selected, adapted, and combined to construct an Agreement tailored to different conflict and security contexts.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Handbook reader intro (Markdown)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>builder.undefined_terms_warning</t>
+          <t>builder.intro_title</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>These capitalized terms are used in your agreement but have no definition:</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>Build Your Own Agreement</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Builder page heading</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>builder.context_change_confirm_title</t>
+          <t>builder.intro</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Change context?</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>Use the Build an Agreement function to create an Agreement tailored to your specific conflict or security context. We recommend reading the [Note to Users](#/handbook/s-note-to-users) before you begin.
+To get started, choose one of two approaches:
+- **Build from scratch:** Select the provisions you wish to include from the left-hand column and add them to your Agreement in the right-hand column.
+- **Start with the full Agreement:** Add all of the Handbook's model provisions to your Agreement, then remove those that are not relevant.
+Either way, once you have selected your provisions, you can edit and adapt the text in the right-hand column to reflect the specific circumstances, priorities, and commitments of the Parties.
+Your Agreement is saved automatically in this browser, and you can come back to it at any time. You will find your saved Agreements in the Drafts box at the top left of the builder.
+You can download your Agreement in various formats: Word, Markdown and PDF.
+A few things to note:
+- Terms that are defined will be included in the Definitions section, which you can add to.
+- Relevant footnotes will also be included in the final Agreement.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Builder intro (Markdown)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>builder.context_change_confirm_body</t>
+          <t>builder.note_banner</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Add this context's suggested provisions and remove unedited suggestions from the old one? Anything you edited, pinned, or added by hand stays.</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>**Read this first:** the [Note to Users](#/handbook/s-note-to-users) explains how the Handbook's provisions fit together and how to adapt them.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Read-me-first banner on the builder (Markdown)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>review.comment_button</t>
+          <t>builder.start_scratch</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>Build from scratch</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Start button</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>review.reply_button</t>
+          <t>builder.start_full</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Reply</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>Start with the full Agreement</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Start button: adds every provision</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>review.reviewing_as</t>
+          <t>builder.drafts_label</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Reviewing as</t>
+          <t>Drafts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>e.g. "Reviewing as Lawyer / legal scholar"</t>
+          <t>Label for the saved-drafts dropdown</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>review.sign_out</t>
+          <t>builder.context_help</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sign out</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>Fills the context wording in your Agreement and suggests relevant International Law commitments.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Tooltip on the context dropdown</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>review.comment_removed</t>
+          <t>builder.context_none</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Comment removed</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Shown in place of a hidden parent comment</t>
+          <t>Context dropdown, no context</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>review.comment_on_earlier_version</t>
+          <t>builder.section_guidance</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>This comment was left on an earlier version of this text.</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>Note to Users for this section</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Library: expandable section guidance</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>review.filter_open_only</t>
+          <t>builder.ac_only_badge</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Open threads only</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>Armed Conflict only</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Library badge on IHL clauses</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>review.register_title</t>
+          <t>builder.empty_agreement</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Become a reviewer</t>
+          <t>Nothing added yet -- browse the library on the left.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1292,12 +1344,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>review.register_pending</t>
+          <t>context.label</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Thanks -- we'll email you once your reviewer access is approved.</t>
+          <t>Context</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1305,291 +1357,54 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>error.rate_limited</t>
+          <t>builder.reorder_hint</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>You're commenting faster than we can keep up. Try again in a minute.</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Maps to Apps Script code rate_limited</t>
-        </is>
-      </c>
+          <t>Drag or use ↑ ↓ to reorder provisions within a section.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>error.invalid_token</t>
+          <t>builder.edit</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Your reviewer link has expired or been revoked. Ask an admin to resend it.</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Maps to code invalid_token</t>
-        </is>
-      </c>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>error.body_too_long</t>
+          <t>builder.move_up</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>That comment is too long (4,000 characters max).</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Maps to code body_too_long</t>
-        </is>
-      </c>
+          <t>Move up within this section</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>error.selection_too_long</t>
+          <t>builder.move_down</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Please select a shorter passage to comment on.</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Maps to code selection_too_long</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>error.network</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Couldn't reach the server. Your comment hasn't been posted -- try again.</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>footer.data_source</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Content is maintained by the Digital Ceasefire Initiative and updates automatically.</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>footer.disclaimer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>This tool assembles model language for discussion. It is not legal advice.</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>token</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>resend</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>approved_at</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>token_hash</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>comment_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>parent_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>token</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>provision_id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>target_type</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>handbook_version</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>selected_text</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>start_offset</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>end_offset</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>body</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>QUERY(reviewers!A:I, "select I, C where D = 'active'", 1)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>QUERY(feedback!A:M, "select A,B,D,E,F,G,H,K,L,M", 1)</f>
-        <v/>
-      </c>
+          <t>Move down within this section</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14647,49 +14462,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The Handbook (working draft v1.4, May 2026) is now browsable online, and you can build your own agreement from its provisions in the Builder.
-Everything here comes straight from the Handbook text -- if you spot something that doesn't match the source, use the reviewer comment tool once you're approved, or reach out to the drafters directly.</t>
+          <t>The Handbook (working draft v1.4, May 2026) is now browsable online, and you can build your own agreement from its provisions in the Builder.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>published</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Email Address</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Why do you want to review?</t>
         </is>
       </c>
     </row>

--- a/Digital Ceasefire Platform.xlsx
+++ b/Digital Ceasefire Platform.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,7 +530,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A practical framework for mediators, negotiators, and affected communities to negotiate, draft, and implement ceasefire, de-escalation, and other agreements to constrain digital operations during conflict and other security contexts.</t>
+          <t>A practical framework for mediators, parties, and affected communities to negotiate, draft, and implement ceasefire, de-escalation, and other agreements to constrain digital operations during conflict and other security contexts.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -982,12 +982,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>builder.undefined_terms_warning</t>
+          <t>footer.data_source</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>These capitalized terms are used in your agreement but have no definition:</t>
+          <t>Content is maintained by the Digital Ceasefire Platform and updates automatically.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -995,12 +995,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>footer.data_source</t>
+          <t>footer.disclaimer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Content is maintained by the Digital Ceasefire Initiative and updates automatically.</t>
+          <t>This tool assembles model language for discussion. It is not legal advice.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -1008,25 +1008,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>footer.disclaimer</t>
+          <t>home.cta_read.desc</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>This tool assembles model language for discussion. It is not legal advice.</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Browse the full text of the Handbook, section by section.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Home card description</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>home.cta_read.desc</t>
+          <t>home.cta_build.desc</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Browse the full text of the Handbook, section by section.</t>
+          <t>Assemble a customized ceasefire, de-escalation, or other agreement from the available provisions.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1038,12 +1042,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>home.cta_build.desc</t>
+          <t>home.cta_updates.desc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Assemble a customized ceasefire, de-escalation, or other agreement from the available provisions.</t>
+          <t>See the latest posts, news and updates to the Platform.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1055,24 +1059,24 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>home.cta_updates.desc</t>
+          <t>nav.about</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>See the latest posts, news and updates to the Platform.</t>
+          <t>About</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Home card description</t>
+          <t>Header nav item</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>nav.about</t>
+          <t>about.title</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1082,34 +1086,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Header nav item</t>
+          <t>About page heading</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>about.title</t>
+          <t>about.body</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
-        <is>
-          <t>About</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>About page heading</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>about.body</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
         <is>
           <t>The Digital Ceasefire &amp; De-escalation Handbook provides a practical framework for mediators, negotiators, and affected communities to negotiate, draft, and implement ceasefire, de-escalation, and other agreements that constrain digital operations in conflict and other security contexts.
 Developed in response to the accelerating digitalization of warfare, the Platform addresses the urgent need to confront hostile digital operations. Ceasefire agreements have traditionally overlooked the digital dimensions of conflict, leaving gaps in civilian protection and allowing unconstrained digital operations to take place.
@@ -1117,8 +1104,8 @@
 Grounded in International Law, including International Humanitarian Law, International Human Rights Law, and International Criminal Law, the Platform recognizes the challenges of applying existing legal frameworks to evolving digital threats. While Parties remain bound by their obligations under International Law, the Platform enables them to negotiate additional commitments to restrain and de-escalate digital operations that may otherwise be lawful.
 At its core is the Digital Ceasefire &amp; De-escalation Handbook, a living resource designed to evolve alongside technological developments, emerging threats, and lessons from practice. Rather than prescribing a single solution, the Handbook offers a flexible menu of model provisions that Parties can select, adapt, and combine to develop agreements tailored to different conflict and security contexts.
 Through the Platform's [Build an Agreement function](#/builder), users can construct customized agreements using the Handbook's model provisions. The [Note to Users](#/handbook/s-note-to-users) provides useful background to constructing an Agreement. Alternatively, the [entire handbook](#/handbook) can be read and used here as a guide to support and contribute to existing negotiations.
-### Background to the Initiative
-The Digital Ceasefire &amp; De-escalation Platform is an initiative of the Human Rights Center at the University of California, Berkeley School of Law, and is co-led by Senior Research Fellow Brett Solomon and Executive Director Betsy Popken. The Handbook has been informed by research, consultations, and engagement with experts and practitioners working across conflict mediation and negotiation, international law, human rights, humanitarian protection, and digital technologies.
+### Background to the Platform
+The [Digital Ceasefire &amp; De-escalation Platform](https://humanrights.berkeley.edu/projects/digital-ceasefire-and-de-escalation-handbook/) is an initiative of the [Human Rights Center](https://humanrights.berkeley.edu/) at the University of California, Berkeley School of Law, and is co-led by Senior Research Fellow [Brett Solomon](https://humanrights.berkeley.edu/people/brett-solomon/) and Executive Director [Betsy Popken](https://humanrights.berkeley.edu/people/betsy-popken/). The Handbook has been informed by research, consultations, and engagement with experts and practitioners working across conflict mediation and negotiation, international law, human rights, humanitarian protection, and digital technologies.
 The initiative seeks to bridge the gap between the rapidly evolving realities of digital warfare and the practical tools available to those working to prevent conflict, reduce hostilities, protect civilians, and advance Digital Peace.
 The Digital Ceasefire team is available to provide advice, technical assistance, briefings, training, and support to mediators, negotiators, civil society organizations, and others addressing the digital dimensions of conflict.
 The website was created by the Investigations Lab, Human Rights Center. **AI Disclosure:** This platform was created using a combination of cloud and local models and LLM harnesses. All the text was produced by humans.
@@ -1126,217 +1113,231 @@
 [Explore the Handbook](#/handbook) | [Build an Agreement](#/builder) | [Request Support](mailto:bpopken@berkeley.edu)</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>About page body (Markdown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>handbook.intro</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>The full text of the Digital Ceasefire &amp; De-escalation Handbook is available here, section by section, or it can be downloaded in full in [PDF format](#handbook-pdf). The Handbook guides users through the process of developing an Agreement, either by selecting appropriate provisions of the Handbook into an Agreement or by using the Platform's [Build an Agreement function](#/builder). We recommend starting with reading the [Note to Users](#/handbook/s-note-to-users) below. Sections 1.0 through 11.0 then provide model provisions that can be selected, adapted, and combined to construct an Agreement tailored to different conflict and security contexts.</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>About page body (Markdown)</t>
+          <t>Handbook reader intro (Markdown)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>handbook.intro</t>
+          <t>builder.intro_title</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The full text of the Digital Ceasefire &amp; De-escalation Handbook is available here, section by section, or it can be downloaded in full in [PDF format](#handbook-pdf). The Handbook guides users through the process of developing an Agreement, either by selecting appropriate provisions of the Handbook into an Agreement or by using the Platform's [Build an Agreement function](#/builder). We recommend starting with reading the [Note to Users](#/handbook/s-note-to-users) below. Sections 1.0 through 11.0 then provide model provisions that can be selected, adapted, and combined to construct an Agreement tailored to different conflict and security contexts.</t>
+          <t>Build Your Own Agreement</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Handbook reader intro (Markdown)</t>
+          <t>Builder page heading</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>builder.intro_title</t>
+          <t>builder.intro</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Build Your Own Agreement</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Builder page heading</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>builder.intro</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
           <t>Use the Build an Agreement function to create an Agreement tailored to your specific conflict or security context. We recommend reading the [Note to Users](#/handbook/s-note-to-users) before you begin.
-To get started, choose one of two approaches:
+To get started, choose one of three approaches:
 - **Build from scratch:** Select the provisions you wish to include from the left-hand column and add them to your Agreement in the right-hand column.
 - **Start with the full Agreement:** Add all of the Handbook's model provisions to your Agreement, then remove those that are not relevant.
+- **Use the Handbook:** Read the [Handbook](#/handbook) section by section and add provisions to your Agreement as you go.
 Either way, once you have selected your provisions, you can edit and adapt the text in the right-hand column to reflect the specific circumstances, priorities, and commitments of the Parties.
 Your Agreement is saved automatically in this browser, and you can come back to it at any time. You will find your saved Agreements in the Drafts box at the top left of the builder.
-You can download your Agreement in various formats: Word, Markdown and PDF.
+You can download your Agreement in various formats: Word, Markdown and PDF, by selecting the format in the Export drop down.
 A few things to note:
 - Terms that are defined will be included in the Definitions section, which you can add to.
 - Relevant footnotes will also be included in the final Agreement.</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Builder intro (Markdown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>builder.note_banner</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>**Read this first:** the [Note to Users](#/handbook/s-note-to-users) explains how the Handbook's provisions fit together and how to adapt them.</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Builder intro (Markdown)</t>
+          <t>Read-me-first banner on the builder (Markdown)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>builder.note_banner</t>
+          <t>builder.start_scratch</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>**Read this first:** the [Note to Users](#/handbook/s-note-to-users) explains how the Handbook's provisions fit together and how to adapt them.</t>
+          <t>Build from scratch</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Read-me-first banner on the builder (Markdown)</t>
+          <t>Start button</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>builder.start_scratch</t>
+          <t>builder.start_full</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Build from scratch</t>
+          <t>Start with the full Agreement</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Start button</t>
+          <t>Start button: adds every provision</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>builder.start_full</t>
+          <t>builder.drafts_label</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Start with the full Agreement</t>
+          <t>Drafts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Start button: adds every provision</t>
+          <t>Label for the saved-drafts dropdown</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>builder.drafts_label</t>
+          <t>builder.context_help</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Drafts</t>
+          <t>Fills the context wording in your Agreement and suggests relevant International Law commitments.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Label for the saved-drafts dropdown</t>
+          <t>Tooltip on the context dropdown</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>builder.context_help</t>
+          <t>builder.context_none</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fills the context wording in your Agreement and suggests relevant International Law commitments.</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tooltip on the context dropdown</t>
+          <t>Context dropdown, no context</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>builder.context_none</t>
+          <t>builder.section_guidance</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>Note to Users for this section</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Context dropdown, no context</t>
+          <t>Library: expandable section guidance</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>builder.section_guidance</t>
+          <t>builder.ac_only_badge</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Note to Users for this section</t>
+          <t>Armed Conflict only</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Library: expandable section guidance</t>
+          <t>Library badge on IHL clauses</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>builder.ac_only_badge</t>
+          <t>builder.empty_agreement</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Armed Conflict only</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Library badge on IHL clauses</t>
-        </is>
-      </c>
+          <t>Nothing added yet -- browse the library on the left.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>builder.empty_agreement</t>
+          <t>context.label</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nothing added yet -- browse the library on the left.</t>
+          <t>Context</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1344,12 +1345,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>context.label</t>
+          <t>builder.reorder_hint</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Context</t>
+          <t>Drag or use ↑ ↓ to reorder provisions within a section.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1357,12 +1358,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>builder.reorder_hint</t>
+          <t>builder.edit</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Drag or use ↑ ↓ to reorder provisions within a section.</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1370,12 +1371,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>builder.edit</t>
+          <t>builder.move_up</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Move up within this section</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1383,28 +1384,15 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>builder.move_up</t>
+          <t>builder.move_down</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Move up within this section</t>
+          <t>Move down within this section</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>builder.move_down</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Move down within this section</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10933,7 +10921,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deliberately misleading or inaccurate information that is intended to deceive and is shared in order to do serious reputational, financial, legal, psychological, or physical injury to persons or result in the damage or destruction of Civilian Objects or Military Objects. This includes information that intends to influence public opinion or obscure the truth. Irony, satire, parody, or humour that seeks to question or ridicule are not forms of Disinformation.</t>
+          <t>Deliberately misleading or inaccurate information that is intended to deceive and is shared in order to do serious reputational, financial, legal, psychological, or physical injury to persons or result in the damage or destruction of Civilian Objects or Military Objectives. This includes information that intends to influence public opinion or obscure the truth. Irony, satire, parody, or humour that seeks to question or ridicule are not forms of Disinformation.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -14404,7 +14392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14442,30 +14430,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>post-2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>It's live: the Digital Ceasefire &amp; De-escalation Platform</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Digital Ceasefire Platform</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>The Digital Ceasefire &amp; De-escalation Platform is now live. You can [read the Handbook](#/handbook) section by section, or [build your own Agreement](#/builder) from its model provisions and download it as Word, Markdown or PDF.
+The Platform is an initiative of the [Human Rights Center](https://humanrights.berkeley.edu/) at UC Berkeley School of Law.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>post-2026-09-18</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>The Digital Ceasefire Platform is live</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Digital Ceasefire Initiative</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>The Handbook (working draft v1.4, May 2026) is now browsable online, and you can build your own agreement from its provisions in the Builder.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Digital Ceasefire Platform</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>The Handbook is now browsable online, and you can build your own Agreement from its provisions in [Build an Agreement](#/builder).</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>post-tpp-true-peace</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>For True Peace, Ceasefires Must Address Digital Warfare Too</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tech Policy Press</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Read the article on [Tech Policy Press](https://www.techpolicy.press/for-true-peace-ceasefires-must-address-digital-warfare-too/).</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>published</t>
         </is>

--- a/Digital Ceasefire Platform.xlsx
+++ b/Digital Ceasefire Platform.xlsx
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The full text of the Digital Ceasefire &amp; De-escalation Handbook is available here, section by section, or it can be downloaded in full in [PDF format](#handbook-pdf). The Handbook guides users through the process of developing an Agreement, either by selecting appropriate provisions of the Handbook into an Agreement or by using the Platform's [Build an Agreement function](#/builder). We recommend starting with reading the [Note to Users](#/handbook/s-note-to-users) below. Sections 1.0 through 11.0 then provide model provisions that can be selected, adapted, and combined to construct an Agreement tailored to different conflict and security contexts.</t>
+          <t>The full text of the Digital Ceasefire &amp; De-escalation Handbook is available here, section by section, or it can be downloaded in full in [PDF format](#handbook-pdf). The Handbook guides users through the process of developing an Agreement, using the Platform's [Build an Agreement function](#/builder). We recommend starting with reading the [Note to Users](#/handbook/s-note-to-users) below. Sections 1.0 through 11.0 then provide model provisions that can be selected, adapted, and combined in [Build an Agreement](#/builder) to construct an Agreement tailored to different conflict and security contexts.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1165,7 +1165,7 @@
 To get started, choose one of three approaches:
 - **Build from scratch:** Select the provisions you wish to include from the left-hand column and add them to your Agreement in the right-hand column.
 - **Start with the full Agreement:** Add all of the Handbook's model provisions to your Agreement, then remove those that are not relevant.
-- **Use the Handbook:** Read the [Handbook](#/handbook) section by section and add provisions to your Agreement as you go.
+- **Use Handbook view:** Read the Handbook section by section and add provisions to your Agreement as you go.
 Either way, once you have selected your provisions, you can edit and adapt the text in the right-hand column to reflect the specific circumstances, priorities, and commitments of the Parties.
 Your Agreement is saved automatically in this browser, and you can come back to it at any time. You will find your saved Agreements in the Drafts box at the top left of the builder.
 You can download your Agreement in various formats: Word, Markdown and PDF, by selecting the format in the Export drop down.

--- a/Digital Ceasefire Platform.xlsx
+++ b/Digital Ceasefire Platform.xlsx
@@ -20919,12 +20919,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OECD Legal Instruments, Recommendation of the Council on Information Integrity, https://legalinstruments.oecd.org/en/instruments/OECD-LEGAL-0505?trk=article-ssr-frontend-pulse_little-text-block&amp;utm_source=chatgpt.com.</t>
+          <t>OECD Legal Instruments, Recommendation of the Council on Information Integrity, https://legalinstruments.oecd.org/en/instruments/OECD-LEGAL-0505?trk=article-ssr-frontend-pulse_little-text-block.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://legalinstruments.oecd.org/en/instruments/OECD-LEGAL-0505?trk=article-ssr-frontend-pulse_little-text-block&amp;utm_source=chatgpt.com</t>
+          <t>https://legalinstruments.oecd.org/en/instruments/OECD-LEGAL-0505?trk=article-ssr-frontend-pulse_little-text-block</t>
         </is>
       </c>
     </row>

--- a/Digital Ceasefire Platform.xlsx
+++ b/Digital Ceasefire Platform.xlsx
@@ -20282,7 +20282,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Organisation for Economic Co-operation and Development (OECD), Explanatory Memorandum on the Updated OECD Definition of an AI System, OECD Artificial Intelligence Papers, no. 8 (Paris: OECD Publishing, 2024), 4, [https://doi.org/10.1787/623da898-en](https://doi.org/10.1787/623da898-en?utm_source=chatgpt.com).</t>
+          <t>Organisation for Economic Co-operation and Development (OECD), Explanatory Memorandum on the Updated OECD Definition of an AI System, OECD Artificial Intelligence Papers, no. 8 (Paris: OECD Publishing, 2024), 4, [https://doi.org/10.1787/623da898-en](https://doi.org/10.1787/623da898-en).</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -21306,7 +21306,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>See *Legality of the Threat or Use of Nuclear Weapons*, Advisory Opinion, July 8, 1996, *I.C.J. Reports* 1996, 226, 244, ¶ 39, [https://www.icj-cij.org/case/95/advisory-opinions](https://www.icj-cij.org/case/95/advisory-opinions?utm_source=chatgpt.com) (providing that Articles 2(4) and 51 “do not refer to specific weapons” and “apply to any use of force, regardless of the weapons employed”).</t>
+          <t>See *Legality of the Threat or Use of Nuclear Weapons*, Advisory Opinion, July 8, 1996, *I.C.J. Reports* 1996, 226, 244, ¶ 39, [https://www.icj-cij.org/case/95/advisory-opinions](https://www.icj-cij.org/case/95/advisory-opinions) (providing that Articles 2(4) and 51 “do not refer to specific weapons” and “apply to any use of force, regardless of the weapons employed”).</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
